--- a/data/warehouse2.xlsx
+++ b/data/warehouse2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\А_Гр\QR_Ilya\QR\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{560D7543-EED6-4B9C-B97D-1917F2F5288F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF968C88-4233-4487-8149-85F8FA08E936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="48345" yWindow="2580" windowWidth="16200" windowHeight="9315" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -84,13 +84,13 @@
     <t>Изображение</t>
   </si>
   <si>
-    <t>Документ</t>
-  </si>
-  <si>
-    <t>Аналог</t>
-  </si>
-  <si>
-    <t>Общее кол-во</t>
+    <t>Текущее кол-во</t>
+  </si>
+  <si>
+    <t>Вложенный документ</t>
+  </si>
+  <si>
+    <t>Аналог/заменитель</t>
   </si>
 </sst>
 </file>
@@ -413,9 +413,10 @@
   <cols>
     <col min="3" max="3" width="36.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.06640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.46484375" customWidth="1"/>
+    <col min="5" max="5" width="14.59765625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="47.796875" customWidth="1"/>
+    <col min="8" max="8" width="20.06640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="37.46484375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -433,7 +434,7 @@
         <v>15</v>
       </c>
       <c r="E1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F1" t="s">
         <v>16</v>
@@ -442,10 +443,10 @@
         <v>17</v>
       </c>
       <c r="H1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
